--- a/Statistics/Section 2 - Descriptive Statistics Fundamentals/11_Covariance/Exercises/2.11.+Covariance_exercise - completed.xlsx
+++ b/Statistics/Section 2 - Descriptive Statistics Fundamentals/11_Covariance/Exercises/2.11.+Covariance_exercise - completed.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\365 Data Science\Statistics\Section 2\11_Covariance\Exercises\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slong\365 Data Science\Statistics_\Section 2 - Descriptive Statistics Fundamentals\11_Covariance_\Exercises\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FACCE7F-E536-4B6B-89D7-8029628501D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3290E81-BDDA-4D7A-A6B7-9F0FCB2D8D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,6 +22,9 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -3045,14 +3048,14 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>320040</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>80010</xdr:rowOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>17664</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>182880</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>102870</xdr:rowOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>33596</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3080,15 +3083,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>373380</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>22860</xdr:rowOff>
+      <xdr:colOff>331818</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>133697</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>236220</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
+      <xdr:colOff>194658</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>126077</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
